--- a/Vlad/export/Приложение_Б.xlsx
+++ b/Vlad/export/Приложение_Б.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -580,70 +580,70 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>169.076</v>
+        <v>227.346</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>187.022</v>
+        <v>236.957</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>204.967</v>
+        <v>246.567</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>218.978</v>
+        <v>252.025</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>207.283</v>
+        <v>242.521</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>199.765</v>
+        <v>232.824</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>-2.415</v>
+        <v>59.156</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>172.12</v>
+        <v>170.785</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>30.757</v>
+        <v>73.01600000000001</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>218.992</v>
+        <v>258.874</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>269.428</v>
+        <v>296.621</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>202.119</v>
+        <v>244.005</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>278.138</v>
+        <v>302.993</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>207.818</v>
+        <v>251.386</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>90.63200000000001</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>50.295</v>
+        <v>54.847</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>81.247</v>
+        <v>72.58799999999999</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>51.934</v>
+        <v>56.283</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>85.88800000000001</v>
+        <v>74.738</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>33.954</v>
+        <v>18.456</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>30.952</v>
+        <v>17.741</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.878</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="3">
@@ -651,70 +651,70 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>204.967</v>
+        <v>246.567</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>218.928</v>
+        <v>255.93</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>232.888</v>
+        <v>265.294</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>207.273</v>
+        <v>237.915</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>195.396</v>
+        <v>227.586</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>189.64</v>
+        <v>220.741</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>24.328</v>
+        <v>63.462</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>182.636</v>
+        <v>185.598</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>47.658</v>
+        <v>77.048</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>208.696</v>
+        <v>246.233</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>267.461</v>
+        <v>293.67</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>195.537</v>
+        <v>233.801</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>274.942</v>
+        <v>300.218</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>198.738</v>
+        <v>238.206</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>83.306</v>
+        <v>75.065</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>46.933</v>
+        <v>50.802</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>75.893</v>
+        <v>70.759</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>48.928</v>
+        <v>52.417</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>79.47799999999999</v>
+        <v>72.827</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>30.55</v>
+        <v>20.41</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>28.96</v>
+        <v>19.956</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.82</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="4">
@@ -722,70 +722,70 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>232.888</v>
+        <v>265.294</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>243.184</v>
+        <v>272.985</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>253.479</v>
+        <v>280.676</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>196.13</v>
+        <v>225.446</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>184.786</v>
+        <v>215.127</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>180.825</v>
+        <v>209.828</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>42.33</v>
+        <v>69.676</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>192.568</v>
+        <v>197.689</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>58.646</v>
+        <v>80.818</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>200.646</v>
+        <v>235.968</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>266.886</v>
+        <v>292.166</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>190.098</v>
+        <v>224.854</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>273.458</v>
+        <v>298.483</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>191.592</v>
+        <v>227.924</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>77.821</v>
+        <v>72.82599999999999</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>43.818</v>
+        <v>47.419</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>72.03100000000001</v>
+        <v>68.935</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>45.826</v>
+        <v>49.052</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>74.682</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>28.856</v>
+        <v>21.658</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>28.212</v>
+        <v>21.516</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.773</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="5">
@@ -793,70 +793,70 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>253.479</v>
+        <v>280.676</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>260.858</v>
+        <v>286.525</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>268.237</v>
+        <v>292.373</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>186.072</v>
+        <v>213.784</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>175.517</v>
+        <v>203.827</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>173.453</v>
+        <v>200.129</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>57.918</v>
+        <v>77.84399999999999</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>197.304</v>
+        <v>204.481</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>69.083</v>
+        <v>86.193</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>194.877</v>
+        <v>227.515</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>264.074</v>
+        <v>288.717</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>186.704</v>
+        <v>217.901</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>269.939</v>
+        <v>294.694</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>186.669</v>
+        <v>219.719</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>72.70999999999999</v>
+        <v>69.992</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>41.656</v>
+        <v>44.908</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>68.283</v>
+        <v>66.699</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43.576</v>
+        <v>46.506</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>70.095</v>
+        <v>68.074</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>26.519</v>
+        <v>21.569</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>26.628</v>
+        <v>21.791</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.725</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -864,70 +864,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>268.237</v>
+        <v>292.373</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>273.745</v>
+        <v>296.884</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>279.254</v>
+        <v>301.395</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>177.746</v>
+        <v>203.447</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>167.733</v>
+        <v>193.752</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>167.164</v>
+        <v>191.385</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>68.473</v>
+        <v>83.723</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>201.197</v>
+        <v>209.957</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>76.571</v>
+        <v>90.104</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>190.479</v>
+        <v>220.001</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>261.944</v>
+        <v>285.695</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>183.866</v>
+        <v>211.535</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>267.394</v>
+        <v>291.42</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>182.75</v>
+        <v>212.359</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>68.932</v>
+        <v>67.63200000000001</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>39.817</v>
+        <v>42.701</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>65.389</v>
+        <v>64.789</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>41.662</v>
+        <v>44.277</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>66.611</v>
+        <v>65.836</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>24.948</v>
+        <v>21.56</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>25.572</v>
+        <v>22.088</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="7">
@@ -935,70 +935,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>279.254</v>
+        <v>301.395</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>283.492</v>
+        <v>304.924</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>287.73</v>
+        <v>308.453</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>170.72</v>
+        <v>194.176</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>161.057</v>
+        <v>184.643</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>161.706</v>
+        <v>183.407</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>76.039</v>
+        <v>87.98399999999999</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>204.383</v>
+        <v>214.45</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>92.94799999999999</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>186.888</v>
+        <v>213.18</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>260.215</v>
+        <v>282.987</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>181.377</v>
+        <v>205.615</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>265.408</v>
+        <v>288.528</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>179.437</v>
+        <v>205.618</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>65.992</v>
+        <v>65.624</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>38.239</v>
+        <v>40.729</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>63.068</v>
+        <v>63.125</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>40.033</v>
+        <v>42.298</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>63.84</v>
+        <v>63.895</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>23.807</v>
+        <v>21.597</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>24.83</v>
+        <v>22.396</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.652</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="8">
@@ -1006,70 +1006,70 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>287.73</v>
+        <v>308.453</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>291.07</v>
+        <v>311.251</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>294.41</v>
+        <v>314.049</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>164.684</v>
+        <v>185.766</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>155.227</v>
+        <v>176.308</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>156.897</v>
+        <v>176.05</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>81.675</v>
+        <v>91.092</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>207.012</v>
+        <v>218.193</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>86.425</v>
+        <v>95.015</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>183.825</v>
+        <v>206.898</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>258.746</v>
+        <v>280.522</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>179.125</v>
+        <v>200.053</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>263.78</v>
+        <v>285.928</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>176.525</v>
+        <v>199.36</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>63.621</v>
+        <v>63.878</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>36.864</v>
+        <v>38.94</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>61.152</v>
+        <v>61.644</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>38.633</v>
+        <v>40.519</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>61.564</v>
+        <v>62.174</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>22.931</v>
+        <v>21.656</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>24.288</v>
+        <v>22.704</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.623</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1077,70 +1077,70 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>294.41</v>
+        <v>314.049</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>297.093</v>
+        <v>316.295</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>299.777</v>
+        <v>318.54</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>159.417</v>
+        <v>178.055</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>150.057</v>
+        <v>168.602</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>152.601</v>
+        <v>169.203</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>85.994</v>
+        <v>93.369</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>209.205</v>
+        <v>221.351</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>89.773</v>
+        <v>96.512</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>181.132</v>
+        <v>201.051</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>257.457</v>
+        <v>278.25</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>177.049</v>
+        <v>194.792</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>262.395</v>
+        <v>283.555</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>173.9</v>
+        <v>193.497</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>61.656</v>
+        <v>62.328</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>35.651</v>
+        <v>37.296</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>59.532</v>
+        <v>60.3</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>37.412</v>
+        <v>38.898</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>59.643</v>
+        <v>60.615</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>22.23</v>
+        <v>21.717</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>23.882</v>
+        <v>23.004</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.599</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="10">
@@ -1148,70 +1148,70 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>299.777</v>
+        <v>318.54</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>301.968</v>
+        <v>320.361</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>304.159</v>
+        <v>322.182</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>154.754</v>
+        <v>170.918</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>145.409</v>
+        <v>161.413</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>148.72</v>
+        <v>162.78</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>89.376</v>
+        <v>95.039</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>211.057</v>
+        <v>224.046</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>92.43899999999999</v>
+        <v>97.587</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>178.709</v>
+        <v>195.564</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>256.299</v>
+        <v>276.135</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>175.107</v>
+        <v>189.79</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>261.184</v>
+        <v>281.364</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>171.49</v>
+        <v>187.965</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>59.992</v>
+        <v>60.924</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>34.565</v>
+        <v>35.771</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>58.136</v>
+        <v>59.057</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>36.335</v>
+        <v>37.406</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>57.986</v>
+        <v>59.175</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>21.651</v>
+        <v>21.769</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>23.571</v>
+        <v>23.287</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.577</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="11">
@@ -1219,70 +1219,70 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>304.159</v>
+        <v>322.182</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>305.973</v>
+        <v>322.182</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>307.787</v>
+        <v>322.182</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>150.575</v>
+        <v>161.359</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>141.182</v>
+        <v>153.154</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>145.175</v>
+        <v>155.802</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>92.072</v>
+        <v>96.262</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>212.638</v>
+        <v>225.92</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>94.59399999999999</v>
+        <v>96.262</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>176.493</v>
+        <v>187.892</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>255.24</v>
+        <v>272.94</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>173.274</v>
+        <v>183.141</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>260.103</v>
+        <v>277.627</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>169.245</v>
+        <v>180.894</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>58.555</v>
+        <v>59.181</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>33.582</v>
+        <v>34.134</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>56.912</v>
+        <v>58.29</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>35.373</v>
+        <v>35.536</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>56.532</v>
+        <v>57.849</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>21.158</v>
+        <v>22.314</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>23.33</v>
+        <v>24.156</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="12">
@@ -1290,70 +1290,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>307.787</v>
+        <v>322.182</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>309.307</v>
+        <v>322.182</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>310.827</v>
+        <v>322.182</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>146.785</v>
+        <v>154.55</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>137.298</v>
+        <v>146.035</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>141.909</v>
+        <v>149.309</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>94.252</v>
+        <v>95.056</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>214.003</v>
+        <v>227.127</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>96.355</v>
+        <v>95.056</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>174.44</v>
+        <v>181.442</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>254.259</v>
+        <v>270.023</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>171.529</v>
+        <v>176.999</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>259.121</v>
+        <v>274.722</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>167.134</v>
+        <v>174.246</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>57.295</v>
+        <v>58.406</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>32.683</v>
+        <v>32.74</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>55.824</v>
+        <v>57.518</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>34.505</v>
+        <v>34.234</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>55.234</v>
+        <v>56.939</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>20.729</v>
+        <v>22.706</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>23.141</v>
+        <v>24.778</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.539</v>
+        <v>0.569</v>
       </c>
     </row>
     <row r="13">
@@ -1361,70 +1361,70 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>310.827</v>
+        <v>322.182</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>310.827</v>
+        <v>322.182</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>310.827</v>
+        <v>322.182</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>140.504</v>
+        <v>147.364</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>132.202</v>
+        <v>138.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>138.127</v>
+        <v>142.413</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>96.035</v>
+        <v>90.869</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>214.792</v>
+        <v>218.425</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>96.035</v>
+        <v>90.869</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>170.189</v>
+        <v>173.128</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>252.216</v>
+        <v>258.629</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>168.232</v>
+        <v>168.934</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>256.665</v>
+        <v>274.266</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>163.402</v>
+        <v>173.046</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>55.647</v>
+        <v>58.341</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>31.612</v>
+        <v>32.376</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>55.19</v>
+        <v>57.459</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>33.19</v>
+        <v>32.5</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>54.004</v>
+        <v>53.159</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>20.814</v>
+        <v>20.659</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>23.579</v>
+        <v>25.083</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.52</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="14">
@@ -1432,141 +1432,70 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>310.827</v>
+        <v>322.182</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>310.827</v>
+        <v>322.182</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>310.827</v>
+        <v>322.182</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>135.923</v>
+        <v>140.624</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>127.246</v>
+        <v>131.384</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>133.733</v>
+        <v>131.384</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>92.5</v>
+        <v>83.66</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>205.894</v>
+        <v>206.304</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>92.5</v>
+        <v>83.66</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>164.412</v>
+        <v>163.628</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>242.042</v>
+        <v>244.588</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>162.606</v>
+        <v>155.759</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>257.181</v>
+        <v>276.89</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>164.932</v>
+        <v>175.185</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>55.764</v>
+        <v>59.251</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>31.717</v>
+        <v>32.491</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>55.329</v>
+        <v>57.513</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>31.905</v>
+        <v>30.522</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>50.489</v>
+        <v>48.588</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>18.584</v>
+        <v>18.066</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>23.613</v>
+        <v>25.022</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.509</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>310.827</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>310.827</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>310.827</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>132.005</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>122.968</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>122.968</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>85.901</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>193.844</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>85.901</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>157.494</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>229.557</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>260.802</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>169.724</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>56.947</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>55.063</v>
-      </c>
-      <c r="S15" s="2" t="n">
-        <v>30.408</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>46.429</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>16.021</v>
-      </c>
-      <c r="V15" s="2" t="n">
-        <v>22.674</v>
-      </c>
-      <c r="W15" s="2" t="n">
-        <v>0.505</v>
+        <v>0.542</v>
       </c>
     </row>
   </sheetData>
@@ -1580,7 +1509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1730,70 +1659,70 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>267.333</v>
+        <v>294.976</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>273.243</v>
+        <v>298.733</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>279.605</v>
+        <v>302.597</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>152.168</v>
+        <v>208.751</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>146.168</v>
+        <v>202.751</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>147.723</v>
+        <v>197.034</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>87.223</v>
+        <v>110.339</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>192.383</v>
+        <v>192.258</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>87.223</v>
+        <v>110.339</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>175.394</v>
+        <v>236.118</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>241.612</v>
+        <v>279.413</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>171.552</v>
+        <v>225.825</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>245.288</v>
+        <v>283.796</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>170.215</v>
+        <v>230.831</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>60.179</v>
+        <v>62.141</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>37.227</v>
+        <v>46.522</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>59.44</v>
+        <v>60.751</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>38.343</v>
+        <v>47.355</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>59.174</v>
+        <v>61.445</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>20.831</v>
+        <v>14.089</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>22.213</v>
+        <v>14.23</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.761</v>
+        <v>0.899</v>
       </c>
     </row>
     <row r="3">
@@ -1801,70 +1730,70 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>279.605</v>
+        <v>302.597</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>284.848</v>
+        <v>306.46</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>290.331</v>
+        <v>310.415</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>147.723</v>
+        <v>197.034</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>141.415</v>
+        <v>190.7</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>144.692</v>
+        <v>189.045</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>89.989</v>
+        <v>107.691</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>200.342</v>
+        <v>202.725</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>89.989</v>
+        <v>107.691</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>172.974</v>
+        <v>224.543</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>245.225</v>
+        <v>278.323</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>170.393</v>
+        <v>217.566</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>248.916</v>
+        <v>282.701</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>167.62</v>
+        <v>219.007</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>58.651</v>
+        <v>61.341</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>35.217</v>
+        <v>43.249</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>58.121</v>
+        <v>60.332</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>36.403</v>
+        <v>44.184</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>57.53</v>
+        <v>60.546</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>21.126</v>
+        <v>16.362</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>22.904</v>
+        <v>17.082</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.734</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="4">
@@ -1872,70 +1801,70 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>290.331</v>
+        <v>310.415</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>294.521</v>
+        <v>313.732</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>298.83</v>
+        <v>317.107</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>144.692</v>
+        <v>189.045</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>138.077</v>
+        <v>182.378</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>142.035</v>
+        <v>182.041</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>91.655</v>
+        <v>105.872</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>207.175</v>
+        <v>211.235</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>91.655</v>
+        <v>105.872</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>171.279</v>
+        <v>216.672</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>248.971</v>
+        <v>279.074</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>169.041</v>
+        <v>210.589</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>252.7</v>
+        <v>283.475</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>165.728</v>
+        <v>210.88</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>57.648</v>
+        <v>60.75</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>33.683</v>
+        <v>40.807</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>57.166</v>
+        <v>59.818</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>34.931</v>
+        <v>41.827</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>56.424</v>
+        <v>59.865</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>21.493</v>
+        <v>18.038</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>23.483</v>
+        <v>19.012</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.709</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1943,70 +1872,70 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>298.83</v>
+        <v>317.107</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>301.988</v>
+        <v>319.712</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>305.203</v>
+        <v>322.348</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>142.035</v>
+        <v>182.041</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>135.112</v>
+        <v>175.041</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>139.595</v>
+        <v>175.609</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>95.443</v>
+        <v>106.759</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>209.76</v>
+        <v>215.589</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>95.443</v>
+        <v>106.759</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>171.124</v>
+        <v>211.036</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>249.508</v>
+        <v>277.701</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>169.104</v>
+        <v>205.514</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>253.324</v>
+        <v>282.166</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>165.423</v>
+        <v>205.029</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>56.1</v>
+        <v>59.61</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>32.787</v>
+        <v>39.074</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>55.639</v>
+        <v>58.703</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>34.103</v>
+        <v>40.177</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>54.763</v>
+        <v>58.621</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>20.659</v>
+        <v>18.443</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>22.852</v>
+        <v>19.629</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.676</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="6">
@@ -2014,70 +1943,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>305.203</v>
+        <v>322.348</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>307.639</v>
+        <v>324.403</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>310.104</v>
+        <v>326.476</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>139.595</v>
+        <v>175.609</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>132.365</v>
+        <v>168.275</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>137.305</v>
+        <v>169.571</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>98.27</v>
+        <v>107.299</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>211.835</v>
+        <v>219.177</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>98.27</v>
+        <v>107.299</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>170.715</v>
+        <v>205.795</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>249.789</v>
+        <v>276.324</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>168.848</v>
+        <v>200.668</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>253.694</v>
+        <v>280.851</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>164.855</v>
+        <v>199.574</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>54.856</v>
+        <v>58.574</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>31.999</v>
+        <v>37.516</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>54.409</v>
+        <v>57.676</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>33.384</v>
+        <v>38.702</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>53.409</v>
+        <v>57.477</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>20.025</v>
+        <v>18.774</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>22.409</v>
+        <v>20.16</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.647</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="7">
@@ -2085,70 +2014,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>310.104</v>
+        <v>326.476</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>312.021</v>
+        <v>328.111</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>313.955</v>
+        <v>329.756</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>137.305</v>
+        <v>169.571</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>129.766</v>
+        <v>161.904</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>135.127</v>
+        <v>163.83</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>100.418</v>
+        <v>107.558</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>213.537</v>
+        <v>222.198</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>100.418</v>
+        <v>107.558</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>170.107</v>
+        <v>200.806</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>249.875</v>
+        <v>274.927</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>168.354</v>
+        <v>195.982</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>253.872</v>
+        <v>279.511</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>164.082</v>
+        <v>194.375</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>53.82</v>
+        <v>57.613</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>31.287</v>
+        <v>36.079</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>53.383</v>
+        <v>56.714</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>32.741</v>
+        <v>37.349</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>52.266</v>
+        <v>56.403</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>19.525</v>
+        <v>19.053</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>22.096</v>
+        <v>20.635</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.621</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="8">
@@ -2156,70 +2085,70 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>313.955</v>
+        <v>329.756</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>315.491</v>
+        <v>331.068</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>317.036</v>
+        <v>332.387</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>135.127</v>
+        <v>163.83</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>127.281</v>
+        <v>155.83</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>133.038</v>
+        <v>158.324</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>102.076</v>
+        <v>107.605</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>214.96</v>
+        <v>224.782</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>102.076</v>
+        <v>107.605</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>169.348</v>
+        <v>196.008</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>249.816</v>
+        <v>273.514</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>167.686</v>
+        <v>191.43</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>253.904</v>
+        <v>278.149</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>163.156</v>
+        <v>189.372</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>52.932</v>
+        <v>56.703</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>30.63</v>
+        <v>34.732</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>52.502</v>
+        <v>55.798</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>32.154</v>
+        <v>36.086</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>51.271</v>
+        <v>55.374</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>19.117</v>
+        <v>19.288</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>21.872</v>
+        <v>21.066</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.598</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="9">
@@ -2227,70 +2156,70 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>317.036</v>
+        <v>332.387</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>318.285</v>
+        <v>333.449</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>319.541</v>
+        <v>334.516</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>133.038</v>
+        <v>158.324</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>124.884</v>
+        <v>149.991</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>131.023</v>
+        <v>153.012</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>103.373</v>
+        <v>107.497</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>216.168</v>
+        <v>227.019</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>103.373</v>
+        <v>107.497</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>168.479</v>
+        <v>191.369</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>249.649</v>
+        <v>272.093</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>166.892</v>
+        <v>186.998</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>253.826</v>
+        <v>276.775</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>162.118</v>
+        <v>184.534</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>52.152</v>
+        <v>55.825</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>30.016</v>
+        <v>33.453</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>51.728</v>
+        <v>54.91</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>31.61</v>
+        <v>34.892</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>50.384</v>
+        <v>54.371</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>18.774</v>
+        <v>19.479</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>21.712</v>
+        <v>21.458</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.578</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="10">
@@ -2298,70 +2227,70 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>319.541</v>
+        <v>334.516</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>320.571</v>
+        <v>335.385</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>321.605</v>
+        <v>336.256</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>131.023</v>
+        <v>153.012</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>122.562</v>
+        <v>144.346</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>129.07</v>
+        <v>147.864</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>104.397</v>
+        <v>107.281</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>217.208</v>
+        <v>228.975</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>104.397</v>
+        <v>107.281</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>167.529</v>
+        <v>186.874</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>249.4</v>
+        <v>270.675</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>166.006</v>
+        <v>182.683</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>253.666</v>
+        <v>275.395</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>160.997</v>
+        <v>179.847</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>51.453</v>
+        <v>54.965</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>29.434</v>
+        <v>32.227</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>51.033</v>
+        <v>54.038</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>31.099</v>
+        <v>33.753</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>49.576</v>
+        <v>53.379</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>18.477</v>
+        <v>19.627</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>21.598</v>
+        <v>21.81</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="11">
@@ -2369,70 +2298,70 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>321.605</v>
+        <v>336.256</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>322.464</v>
+        <v>335.569</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>323.326</v>
+        <v>334.884</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>129.07</v>
+        <v>147.864</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>120.301</v>
+        <v>138.864</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>127.171</v>
+        <v>141.779</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>105.213</v>
+        <v>105.072</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>218.113</v>
+        <v>229.812</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>105.213</v>
+        <v>105.072</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>166.52</v>
+        <v>181.395</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>249.09</v>
+        <v>268.509</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>165.052</v>
+        <v>176.469</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>253.441</v>
+        <v>273.272</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>159.819</v>
+        <v>174.136</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>50.814</v>
+        <v>54.603</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>28.879</v>
+        <v>31.143</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>50.398</v>
+        <v>53.458</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>30.615</v>
+        <v>32.758</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>48.828</v>
+        <v>52.887</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>18.212</v>
+        <v>20.129</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>21.519</v>
+        <v>22.315</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.542</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="12">
@@ -2440,70 +2369,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>323.326</v>
+        <v>334.884</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>324.051</v>
+        <v>334.302</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>324.777</v>
+        <v>333.722</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>127.171</v>
+        <v>141.779</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>118.094</v>
+        <v>132.445</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>125.319</v>
+        <v>136.047</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>105.867</v>
+        <v>103.109</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>218.911</v>
+        <v>230.613</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>105.867</v>
+        <v>103.109</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>165.47</v>
+        <v>175.307</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>248.733</v>
+        <v>265.94</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>164.05</v>
+        <v>170.705</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>253.168</v>
+        <v>270.709</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>158.6</v>
+        <v>167.849</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>50.223</v>
+        <v>53.973</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>28.345</v>
+        <v>29.87</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>49.81</v>
+        <v>52.842</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>30.153</v>
+        <v>31.583</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>48.125</v>
+        <v>52.099</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>17.972</v>
+        <v>20.516</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>21.464</v>
+        <v>22.972</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.526</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2511,70 +2440,70 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>324.777</v>
+        <v>333.722</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>324.165</v>
+        <v>333.265</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>323.554</v>
+        <v>332.809</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>125.319</v>
+        <v>136.047</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>115.934</v>
+        <v>126.38</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>122.648</v>
+        <v>130.667</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>104.734</v>
+        <v>98.00700000000001</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>218.82</v>
+        <v>221.49</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>104.734</v>
+        <v>98.00700000000001</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>163.321</v>
+        <v>167.673</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>247.634</v>
+        <v>255.009</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>161.281</v>
+        <v>163.338</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>252.164</v>
+        <v>271.368</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>156.236</v>
+        <v>168.416</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>50.113</v>
+        <v>54.231</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>27.915</v>
+        <v>29.709</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>49.505</v>
+        <v>53.128</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>29.8</v>
+        <v>30.088</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>47.906</v>
+        <v>48.625</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>18.106</v>
+        <v>18.537</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>21.589</v>
+        <v>23.42</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.511</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="14">
@@ -2582,141 +2511,70 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>323.554</v>
+        <v>332.809</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>323.07</v>
+        <v>332.591</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>322.588</v>
+        <v>332.372</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>122.648</v>
+        <v>130.667</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>112.956</v>
+        <v>120.667</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>120.216</v>
+        <v>120.667</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>100.212</v>
+        <v>90.126</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>209.472</v>
+        <v>209.009</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>100.212</v>
+        <v>90.126</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>158.382</v>
+        <v>158.734</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>237.987</v>
+        <v>241.341</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>156.507</v>
+        <v>150.61</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>253.956</v>
+        <v>275.24</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>159.856</v>
+        <v>172.566</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>50.749</v>
+        <v>55.405</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>28.335</v>
+        <v>29.999</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>50.186</v>
+        <v>53.244</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>28.878</v>
+        <v>28.342</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>44.96</v>
+        <v>44.367</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>16.081</v>
+        <v>16.025</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>21.85</v>
+        <v>23.245</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.502</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>322.588</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>322.505</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>322.421</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>120.216</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>110.216</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>110.216</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>93.059</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>197.12</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>93.059</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>152.026</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>225.841</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>144.248</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>258.958</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>166.877</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>52.257</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>29.211</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>49.825</v>
-      </c>
-      <c r="S15" s="2" t="n">
-        <v>27.66</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>41.335</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>13.675</v>
-      </c>
-      <c r="V15" s="2" t="n">
-        <v>20.614</v>
-      </c>
-      <c r="W15" s="2" t="n">
-        <v>0.501</v>
+        <v>0.539</v>
       </c>
     </row>
   </sheetData>
@@ -2730,7 +2588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2880,70 +2738,70 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>71.214</v>
+        <v>167.906</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>57.284</v>
+        <v>160.385</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>61.142</v>
+        <v>153.093</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>125.6</v>
+        <v>139.446</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>212.552</v>
+        <v>210.318</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>125.6</v>
+        <v>139.446</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>144.384</v>
+        <v>218.26</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>220.136</v>
+        <v>264.494</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>139.691</v>
+        <v>207.081</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>224.165</v>
+        <v>269.121</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>138.046</v>
+        <v>212.529</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>29.553</v>
+        <v>50.29</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>15.083</v>
+        <v>37.328</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>25.957</v>
+        <v>47.671</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>18.523</v>
+        <v>38.602</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>24.517</v>
+        <v>48.995</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>5.994</v>
+        <v>10.393</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>10.874</v>
+        <v>10.342</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="3">
@@ -2951,70 +2809,70 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>82.43000000000001</v>
+        <v>160.729</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>70.504</v>
+        <v>152.899</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>76.866</v>
+        <v>150.829</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>121.703</v>
+        <v>132.711</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>216.45</v>
+        <v>217.053</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>121.703</v>
+        <v>132.711</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>146.99</v>
+        <v>208.437</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>227.643</v>
+        <v>265.5</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>143.944</v>
+        <v>200.902</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>231.614</v>
+        <v>270.085</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>140.65</v>
+        <v>202.46</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>34.11</v>
+        <v>50.454</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>18.042</v>
+        <v>35.162</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>32.276</v>
+        <v>48.656</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>20.848</v>
+        <v>36.52</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>30.084</v>
+        <v>49.043</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>9.236000000000001</v>
+        <v>12.523</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>14.234</v>
+        <v>13.494</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.678</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -3022,70 +2880,70 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>91.718</v>
+        <v>157.636</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>80.879</v>
+        <v>149.576</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>87.46599999999999</v>
+        <v>149.164</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>118.033</v>
+        <v>127.119</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>220.119</v>
+        <v>222.645</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>118.033</v>
+        <v>127.119</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>149.479</v>
+        <v>202.505</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>234.508</v>
+        <v>268.223</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>146.908</v>
+        <v>195.983</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>238.463</v>
+        <v>272.8</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>143.085</v>
+        <v>196.296</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>37.849</v>
+        <v>51.117</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>20.175</v>
+        <v>33.894</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>36.54</v>
+        <v>49.562</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>22.62</v>
+        <v>35.299</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>34.42</v>
+        <v>49.64</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>11.8</v>
+        <v>14.341</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>16.364</v>
+        <v>15.668</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.665</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="5">
@@ -3093,70 +2951,70 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>97.85299999999999</v>
+        <v>154.68</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>87.501</v>
+        <v>146.377</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>94.276</v>
+        <v>147.055</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>117.487</v>
+        <v>124.732</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>220.665</v>
+        <v>225.032</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>117.487</v>
+        <v>124.732</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>152.9</v>
+        <v>198.705</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>237.38</v>
+        <v>268.45</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>150.636</v>
+        <v>192.83</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>241.388</v>
+        <v>273.066</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>146.491</v>
+        <v>192.313</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>39.79</v>
+        <v>51.118</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>21.63</v>
+        <v>33.043</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>38.745</v>
+        <v>49.696</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>23.915</v>
+        <v>34.503</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>36.678</v>
+        <v>49.565</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>12.763</v>
+        <v>15.061</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>17.115</v>
+        <v>16.653</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.641</v>
+        <v>0.743</v>
       </c>
     </row>
     <row r="6">
@@ -3164,70 +3022,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>101.96</v>
+        <v>151.541</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>91.81100000000001</v>
+        <v>142.978</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>98.801</v>
+        <v>144.5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>117.003</v>
+        <v>122.667</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>221.149</v>
+        <v>227.096</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>117.003</v>
+        <v>122.667</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>155.195</v>
+        <v>194.966</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>239.45</v>
+        <v>268.357</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>153.138</v>
+        <v>189.546</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>243.521</v>
+        <v>273.015</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>148.725</v>
+        <v>188.388</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>41.07</v>
+        <v>51.011</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>22.546</v>
+        <v>32.194</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>40.179</v>
+        <v>49.672</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>24.752</v>
+        <v>33.715</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>38.121</v>
+        <v>49.372</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>13.369</v>
+        <v>15.657</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>17.633</v>
+        <v>17.478</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.619</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="7">
@@ -3235,70 +3093,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>104.705</v>
+        <v>148.177</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>94.60299999999999</v>
+        <v>139.338</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>101.832</v>
+        <v>141.571</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>116.563</v>
+        <v>120.841</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>221.589</v>
+        <v>228.923</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>116.563</v>
+        <v>120.841</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>156.685</v>
+        <v>191.204</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>240.938</v>
+        <v>267.994</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>154.78</v>
+        <v>186.131</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>245.081</v>
+        <v>272.694</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>150.123</v>
+        <v>184.439</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>41.932</v>
+        <v>50.802</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>23.119</v>
+        <v>31.328</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>41.141</v>
+        <v>49.517</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>25.292</v>
+        <v>32.914</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>39.063</v>
+        <v>49.067</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>13.771</v>
+        <v>16.152</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>18.022</v>
+        <v>18.189</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.598</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="8">
@@ -3306,70 +3164,70 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>106.498</v>
+        <v>144.614</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>96.348</v>
+        <v>135.484</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>103.835</v>
+        <v>138.346</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>116.159</v>
+        <v>119.204</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>221.993</v>
+        <v>230.56</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>116.159</v>
+        <v>119.204</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>157.59</v>
+        <v>187.411</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>242</v>
+        <v>267.42</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>155.803</v>
+        <v>182.618</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>246.217</v>
+        <v>272.16</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>150.917</v>
+        <v>180.46</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>42.516</v>
+        <v>50.502</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>23.462</v>
+        <v>30.44</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>41.794</v>
+        <v>49.251</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>25.629</v>
+        <v>32.097</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>39.674</v>
+        <v>48.657</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>14.045</v>
+        <v>16.56</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>18.332</v>
+        <v>18.811</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.579</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="9">
@@ -3377,70 +3235,70 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>107.606</v>
+        <v>140.889</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>97.34399999999999</v>
+        <v>131.455</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>105.104</v>
+        <v>134.893</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>115.783</v>
+        <v>117.726</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>222.369</v>
+        <v>232.038</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>115.783</v>
+        <v>117.726</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>158.065</v>
+        <v>183.601</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>242.743</v>
+        <v>266.687</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>156.373</v>
+        <v>179.04</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>247.037</v>
+        <v>271.461</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>151.266</v>
+        <v>176.465</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>42.904</v>
+        <v>50.118</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>23.642</v>
+        <v>29.533</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>42.232</v>
+        <v>48.887</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>25.823</v>
+        <v>31.265</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>40.055</v>
+        <v>48.154</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>14.233</v>
+        <v>16.888</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>18.59</v>
+        <v>19.355</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="10">
@@ -3448,70 +3306,70 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>108.206</v>
+        <v>137.038</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>97.79000000000001</v>
+        <v>127.288</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>105.833</v>
+        <v>131.265</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>115.431</v>
+        <v>116.385</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>222.721</v>
+        <v>233.379</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>115.431</v>
+        <v>116.385</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>158.218</v>
+        <v>179.791</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>243.244</v>
+        <v>265.834</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>156.604</v>
+        <v>175.431</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>247.615</v>
+        <v>270.638</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>151.285</v>
+        <v>172.476</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>43.15</v>
+        <v>49.659</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>23.705</v>
+        <v>28.609</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>42.516</v>
+        <v>48.438</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>25.912</v>
+        <v>30.421</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>40.27</v>
+        <v>47.562</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>14.358</v>
+        <v>17.141</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>18.811</v>
+        <v>19.83</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.545</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="11">
@@ -3519,70 +3377,70 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>338.152</v>
+        <v>349.764</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>338.152</v>
+        <v>348.443</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>338.152</v>
+        <v>347.121</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>108.424</v>
+        <v>129.5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>97.821</v>
+        <v>121.041</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>106.156</v>
+        <v>126.207</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>115.101</v>
+        <v>115.165</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>223.051</v>
+        <v>234.165</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>115.101</v>
+        <v>113.389</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>158.126</v>
+        <v>173.301</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>243.559</v>
+        <v>263.598</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>156.58</v>
+        <v>169.662</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>248.007</v>
+        <v>267.968</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>151.053</v>
+        <v>166.464</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>43.289</v>
+        <v>48.353</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>23.68</v>
+        <v>27.335</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>42.685</v>
+        <v>48.062</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>25.924</v>
+        <v>28.899</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>40.36</v>
+        <v>46.646</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>14.436</v>
+        <v>17.747</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>19.005</v>
+        <v>20.728</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.53</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="12">
@@ -3590,70 +3448,70 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>338.152</v>
+        <v>347.121</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>338.152</v>
+        <v>345.998</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>338.152</v>
+        <v>344.875</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>108.347</v>
+        <v>124.658</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>97.53400000000001</v>
+        <v>115.626</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>106.167</v>
+        <v>121.344</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>114.79</v>
+        <v>112.269</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>223.362</v>
+        <v>234.489</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>114.79</v>
+        <v>110.747</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>157.847</v>
+        <v>167.762</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>243.729</v>
+        <v>261.447</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>156.359</v>
+        <v>164.284</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>248.254</v>
+        <v>265.885</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>150.631</v>
+        <v>160.635</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>43.346</v>
+        <v>47.993</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>23.589</v>
+        <v>26.248</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>42.765</v>
+        <v>47.614</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>25.877</v>
+        <v>27.959</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>40.354</v>
+        <v>46.038</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>14.477</v>
+        <v>18.079</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>19.176</v>
+        <v>21.366</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.516</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="13">
@@ -3661,70 +3519,70 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>338.152</v>
+        <v>344.875</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>336.975</v>
+        <v>343.991</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>335.798</v>
+        <v>343.107</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>104.282</v>
+        <v>121.412</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>94.911</v>
+        <v>111.735</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>104.909</v>
+        <v>117.756</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>114.496</v>
+        <v>105.959</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>223.258</v>
+        <v>224.85</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>112.936</v>
+        <v>104.803</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>154.868</v>
+        <v>161.146</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>242.595</v>
+        <v>251.082</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>154.144</v>
+        <v>157.64</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>246.773</v>
+        <v>267.996</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>148.12</v>
+        <v>163.338</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>42.327</v>
+        <v>48.888</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>23.031</v>
+        <v>26.424</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>42.89</v>
+        <v>48.331</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>24.998</v>
+        <v>26.939</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>39.849</v>
+        <v>43.163</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>14.852</v>
+        <v>16.224</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>19.859</v>
+        <v>21.907</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.499</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="14">
@@ -3732,141 +3590,70 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>335.798</v>
+        <v>343.107</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>334.866</v>
+        <v>342.683</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>333.934</v>
+        <v>342.259</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>105.047</v>
+        <v>118.9</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>95.075</v>
+        <v>108.359</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>104.973</v>
+        <v>108.901</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>108.702</v>
+        <v>96.816</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>213.363</v>
+        <v>211.86</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>107.514</v>
+        <v>96.292</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>151.165</v>
+        <v>153.332</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>233.587</v>
+        <v>237.963</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>150.262</v>
+        <v>145.367</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>250.215</v>
+        <v>273.489</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>154.28</v>
+        <v>169.871</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>44.02</v>
+        <v>50.845</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>24.018</v>
+        <v>27.088</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>44.315</v>
+        <v>48.516</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>24.824</v>
+        <v>25.769</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>38.043</v>
+        <v>39.635</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>13.219</v>
+        <v>13.865</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>20.297</v>
+        <v>21.428</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.494</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>333.934</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>333.774</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>333.613</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>106.731</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>95.55500000000001</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>95.782</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>100.033</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>200.459</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>99.84</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>146.281</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>222.069</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>138.355</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>257.102</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>164.023</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>46.855</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>25.486</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>43.811</v>
-      </c>
-      <c r="S15" s="2" t="n">
-        <v>24.528</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>35.632</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>11.104</v>
-      </c>
-      <c r="V15" s="2" t="n">
-        <v>18.325</v>
-      </c>
-      <c r="W15" s="2" t="n">
-        <v>0.497</v>
+        <v>0.535</v>
       </c>
     </row>
   </sheetData>
